--- a/マイク料金表.xlsx
+++ b/マイク料金表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SLTY\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SLTY\Desktop\mic-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2811E184-90B8-42EA-A3AC-2863AC900DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BD4A03-7326-4696-AAF7-AA906BA92BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{BD0FD287-6373-454C-8CFD-DB7F90A907F7}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="22">
   <si>
     <t>追加ワイヤレスマイク</t>
     <rPh sb="0" eb="2">
@@ -645,7 +645,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -871,26 +871,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1615,7 +1603,7 @@
       <c r="P9" s="10">
         <v>60000</v>
       </c>
-      <c r="Q9" s="76">
+      <c r="Q9" s="75">
         <v>45000</v>
       </c>
       <c r="R9" s="56">
@@ -1665,7 +1653,7 @@
       <c r="P10" s="10">
         <v>60000</v>
       </c>
-      <c r="Q10" s="76">
+      <c r="Q10" s="75">
         <v>45000</v>
       </c>
       <c r="R10" s="56">
@@ -3575,12 +3563,12 @@
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="P50" s="75" t="s">
+      <c r="P50" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="Q50" s="75"/>
-      <c r="R50" s="75"/>
-      <c r="S50" s="75"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="77"/>
+      <c r="S50" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3862,7 +3850,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="77">
+      <c r="M7" s="2">
         <v>45000</v>
       </c>
       <c r="N7" s="11">
@@ -3904,7 +3892,7 @@
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="77">
+      <c r="M8" s="2">
         <v>45000</v>
       </c>
       <c r="N8" s="11">
@@ -3946,7 +3934,7 @@
         <v>40000</v>
       </c>
       <c r="L9" s="10"/>
-      <c r="M9" s="77">
+      <c r="M9" s="2">
         <v>45000</v>
       </c>
       <c r="N9" s="11">
@@ -3988,7 +3976,7 @@
         <v>40000</v>
       </c>
       <c r="L10" s="10"/>
-      <c r="M10" s="77">
+      <c r="M10" s="2">
         <v>45000</v>
       </c>
       <c r="N10" s="11">
@@ -4030,7 +4018,7 @@
       <c r="L11" s="10">
         <v>60000</v>
       </c>
-      <c r="M11" s="77">
+      <c r="M11" s="2">
         <v>45000</v>
       </c>
       <c r="N11" s="11">
@@ -4072,7 +4060,7 @@
       <c r="L12" s="10">
         <v>60000</v>
       </c>
-      <c r="M12" s="77">
+      <c r="M12" s="2">
         <v>45000</v>
       </c>
       <c r="N12" s="11">
@@ -4114,7 +4102,7 @@
       <c r="L13" s="10">
         <v>60000</v>
       </c>
-      <c r="M13" s="77">
+      <c r="M13" s="2">
         <v>45000</v>
       </c>
       <c r="N13" s="11">
@@ -4156,7 +4144,7 @@
       <c r="L14" s="10">
         <v>60000</v>
       </c>
-      <c r="M14" s="77">
+      <c r="M14" s="2">
         <v>45000</v>
       </c>
       <c r="N14" s="62">
@@ -4202,7 +4190,7 @@
         <v>40000</v>
       </c>
       <c r="L15" s="9"/>
-      <c r="M15" s="79">
+      <c r="M15" s="8">
         <v>45000</v>
       </c>
       <c r="N15" s="11">
@@ -4248,7 +4236,7 @@
         <v>40000</v>
       </c>
       <c r="L16" s="10"/>
-      <c r="M16" s="77">
+      <c r="M16" s="2">
         <v>45000</v>
       </c>
       <c r="N16" s="11">
@@ -4294,7 +4282,7 @@
       <c r="L17" s="10">
         <v>60000</v>
       </c>
-      <c r="M17" s="77">
+      <c r="M17" s="2">
         <v>45000</v>
       </c>
       <c r="N17" s="11">
@@ -4340,7 +4328,7 @@
       <c r="L18" s="10">
         <v>60000</v>
       </c>
-      <c r="M18" s="77">
+      <c r="M18" s="2">
         <v>45000</v>
       </c>
       <c r="N18" s="11">
@@ -4386,7 +4374,7 @@
       <c r="L19" s="10">
         <v>60000</v>
       </c>
-      <c r="M19" s="77">
+      <c r="M19" s="2">
         <v>45000</v>
       </c>
       <c r="N19" s="11">
@@ -4432,7 +4420,7 @@
         <v>40000</v>
       </c>
       <c r="L20" s="9"/>
-      <c r="M20" s="77">
+      <c r="M20" s="2">
         <v>45000</v>
       </c>
       <c r="N20" s="11">
@@ -4478,7 +4466,7 @@
         <v>40000</v>
       </c>
       <c r="L21" s="10"/>
-      <c r="M21" s="77">
+      <c r="M21" s="2">
         <v>45000</v>
       </c>
       <c r="N21" s="11">
@@ -4524,7 +4512,7 @@
       <c r="L22" s="10">
         <v>60000</v>
       </c>
-      <c r="M22" s="77">
+      <c r="M22" s="2">
         <v>45000</v>
       </c>
       <c r="N22" s="11">
@@ -4570,7 +4558,7 @@
       <c r="L23" s="19">
         <v>60000</v>
       </c>
-      <c r="M23" s="77">
+      <c r="M23" s="2">
         <v>45000</v>
       </c>
       <c r="N23" s="66">
@@ -4583,24 +4571,24 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
-      <c r="J24" s="78"/>
-      <c r="M24" s="75" t="s">
+      <c r="J24" s="76"/>
+      <c r="M24" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="N24" s="75"/>
-      <c r="O24" s="75"/>
+      <c r="N24" s="77"/>
+      <c r="O24" s="77"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="J25" s="78"/>
+      <c r="J25" s="76"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="J26" s="78"/>
+      <c r="J26" s="76"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="J27" s="78"/>
+      <c r="J27" s="76"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="J28" s="78"/>
+      <c r="J28" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4930,7 +4918,7 @@
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="10"/>
-      <c r="Q7" s="77">
+      <c r="Q7" s="2">
         <v>45000</v>
       </c>
       <c r="R7" s="11">
@@ -4980,7 +4968,7 @@
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="77">
+      <c r="Q8" s="2">
         <v>45000</v>
       </c>
       <c r="R8" s="11">
@@ -5026,7 +5014,7 @@
         <v>40000</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="77">
+      <c r="Q9" s="2">
         <v>45000</v>
       </c>
       <c r="R9" s="11">
@@ -5072,7 +5060,7 @@
         <v>40000</v>
       </c>
       <c r="P10" s="10"/>
-      <c r="Q10" s="77">
+      <c r="Q10" s="2">
         <v>45000</v>
       </c>
       <c r="R10" s="11">
@@ -5122,7 +5110,7 @@
       <c r="P11" s="10">
         <v>60000</v>
       </c>
-      <c r="Q11" s="77">
+      <c r="Q11" s="2">
         <v>45000</v>
       </c>
       <c r="R11" s="11">
@@ -5172,7 +5160,7 @@
       <c r="P12" s="10">
         <v>60000</v>
       </c>
-      <c r="Q12" s="77">
+      <c r="Q12" s="2">
         <v>45000</v>
       </c>
       <c r="R12" s="11">
@@ -5222,7 +5210,7 @@
       <c r="P13" s="10">
         <v>60000</v>
       </c>
-      <c r="Q13" s="77">
+      <c r="Q13" s="2">
         <v>45000</v>
       </c>
       <c r="R13" s="11">
@@ -5272,7 +5260,7 @@
       <c r="P14" s="10">
         <v>60000</v>
       </c>
-      <c r="Q14" s="77">
+      <c r="Q14" s="2">
         <v>45000</v>
       </c>
       <c r="R14" s="11">
@@ -5322,7 +5310,7 @@
         <v>40000</v>
       </c>
       <c r="P15" s="9"/>
-      <c r="Q15" s="79">
+      <c r="Q15" s="8">
         <v>45000</v>
       </c>
       <c r="R15" s="11">
@@ -5377,7 +5365,7 @@
         <v>40000</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="77">
+      <c r="Q16" s="2">
         <v>45000</v>
       </c>
       <c r="R16" s="11">
@@ -5431,7 +5419,7 @@
       <c r="P17" s="10">
         <v>60000</v>
       </c>
-      <c r="Q17" s="79">
+      <c r="Q17" s="8">
         <v>45000</v>
       </c>
       <c r="R17" s="11">
@@ -5485,7 +5473,7 @@
       <c r="P18" s="10">
         <v>60000</v>
       </c>
-      <c r="Q18" s="77">
+      <c r="Q18" s="2">
         <v>45000</v>
       </c>
       <c r="R18" s="11">
@@ -5539,7 +5527,7 @@
       <c r="P19" s="10">
         <v>60000</v>
       </c>
-      <c r="Q19" s="79">
+      <c r="Q19" s="8">
         <v>45000</v>
       </c>
       <c r="R19" s="11">
@@ -5589,7 +5577,7 @@
         <v>40000</v>
       </c>
       <c r="P20" s="10"/>
-      <c r="Q20" s="77">
+      <c r="Q20" s="2">
         <v>45000</v>
       </c>
       <c r="R20" s="11">
@@ -5639,7 +5627,7 @@
         <v>40000</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="79">
+      <c r="Q21" s="8">
         <v>45000</v>
       </c>
       <c r="R21" s="11">
@@ -5689,7 +5677,7 @@
       <c r="P22" s="10">
         <v>60000</v>
       </c>
-      <c r="Q22" s="77">
+      <c r="Q22" s="2">
         <v>45000</v>
       </c>
       <c r="R22" s="11">
@@ -5739,7 +5727,7 @@
       <c r="P23" s="19">
         <v>60000</v>
       </c>
-      <c r="Q23" s="79">
+      <c r="Q23" s="8">
         <v>45000</v>
       </c>
       <c r="R23" s="66">
@@ -5751,24 +5739,24 @@
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="N24" s="78"/>
-      <c r="Q24" s="75" t="s">
+      <c r="N24" s="76"/>
+      <c r="Q24" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="77"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="N25" s="78"/>
+      <c r="N25" s="76"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="N26" s="78"/>
+      <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="N27" s="78"/>
+      <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="N28" s="78"/>
+      <c r="N28" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5785,7 +5773,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.5" customWidth="1"/>
@@ -5860,7 +5848,7 @@
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="44">
-        <f t="shared" ref="C2:C19" si="0">SUM(A2:B2)</f>
+        <f t="shared" ref="C2:C21" si="0">SUM(A2:B2)</f>
         <v>1</v>
       </c>
       <c r="D2" s="6">
@@ -5868,12 +5856,12 @@
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="47">
-        <f t="shared" ref="F2:F19" si="1">SUM(D2:E2)</f>
+        <f t="shared" ref="F2:F21" si="1">SUM(D2:E2)</f>
         <v>2</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="51">
-        <f t="shared" ref="H2:H19" si="2">SUM(G2:G2)</f>
+        <f t="shared" ref="H2:H21" si="2">SUM(G2:G2)</f>
         <v>0</v>
       </c>
       <c r="I2" s="8">
@@ -5931,7 +5919,7 @@
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="11">
-        <f t="shared" ref="Q3:Q19" si="3">SUM(I3:P3)</f>
+        <f t="shared" ref="Q3:Q21" si="3">SUM(I3:P3)</f>
         <v>28500</v>
       </c>
       <c r="R3" s="59"/>
@@ -6100,61 +6088,59 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>40000</v>
-      </c>
+      <c r="M7" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="10"/>
       <c r="P7" s="42"/>
       <c r="Q7" s="11">
         <f t="shared" si="3"/>
-        <v>72500</v>
-      </c>
-      <c r="R7" s="59" t="s">
-        <v>17</v>
-      </c>
+        <v>42500</v>
+      </c>
+      <c r="R7" s="59"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A8" s="12">
-        <v>1</v>
-      </c>
-      <c r="B8" s="28"/>
+      <c r="A8" s="13">
+        <v>1</v>
+      </c>
+      <c r="B8" s="28">
+        <v>6</v>
+      </c>
       <c r="C8" s="44">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="C8" si="4">SUM(A8:B8)</f>
+        <v>7</v>
       </c>
       <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="47">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f t="shared" ref="F8" si="5">SUM(D8:E8)</f>
+        <v>2</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H8" si="6">SUM(G8:G8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="8">
-        <v>15000</v>
-      </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="2">
-        <v>25000</v>
-      </c>
+      <c r="I8" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J8" s="32">
+        <v>21000</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="10"/>
       <c r="P8" s="42"/>
       <c r="Q8" s="11">
-        <f t="shared" si="3"/>
-        <v>50000</v>
+        <f t="shared" ref="Q8" si="7">SUM(I8:P8)</f>
+        <v>56000</v>
       </c>
       <c r="R8" s="59" t="s">
         <v>17</v>
@@ -6164,43 +6150,43 @@
       <c r="A9" s="13">
         <v>1</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="28">
+        <v>7</v>
+      </c>
       <c r="C9" s="44">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="C9" si="8">SUM(A9:B9)</f>
+        <v>8</v>
       </c>
       <c r="D9" s="4">
         <v>2</v>
       </c>
-      <c r="E9" s="4">
-        <v>2</v>
-      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="47">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" ref="F9" si="9">SUM(D9:E9)</f>
+        <v>2</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="51">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H9" si="10">SUM(G9:G9)</f>
         <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>15000</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="2">
-        <v>50000</v>
-      </c>
+      <c r="J9" s="32">
+        <v>24500</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="10"/>
       <c r="P9" s="42"/>
       <c r="Q9" s="11">
-        <f t="shared" si="3"/>
-        <v>75000</v>
+        <f t="shared" ref="Q9" si="11">SUM(I9:P9)</f>
+        <v>59500</v>
       </c>
       <c r="R9" s="59" t="s">
         <v>17</v>
@@ -6219,11 +6205,11 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="47">
+        <f t="shared" si="1"/>
         <v>3</v>
-      </c>
-      <c r="F10" s="47">
-        <f t="shared" si="1"/>
-        <v>5</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="51">
@@ -6235,7 +6221,7 @@
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="2">
-        <v>75000</v>
+        <v>25000</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
@@ -6246,7 +6232,7 @@
       <c r="P10" s="42"/>
       <c r="Q10" s="11">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="R10" s="59" t="s">
         <v>17</v>
@@ -6265,11 +6251,11 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="47">
+        <f t="shared" si="1"/>
         <v>4</v>
-      </c>
-      <c r="F11" s="47">
-        <f t="shared" si="1"/>
-        <v>6</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="51">
@@ -6281,7 +6267,7 @@
       </c>
       <c r="J11" s="32"/>
       <c r="K11" s="2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
@@ -6292,7 +6278,7 @@
       <c r="P11" s="42"/>
       <c r="Q11" s="11">
         <f t="shared" si="3"/>
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="R11" s="59" t="s">
         <v>17</v>
@@ -6311,11 +6297,11 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="47">
+        <f t="shared" si="1"/>
         <v>5</v>
-      </c>
-      <c r="F12" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="51">
@@ -6327,7 +6313,7 @@
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="2">
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -6335,12 +6321,10 @@
         <v>40000</v>
       </c>
       <c r="O12" s="10"/>
-      <c r="P12" s="80">
-        <v>45000</v>
-      </c>
+      <c r="P12" s="42"/>
       <c r="Q12" s="11">
         <f t="shared" si="3"/>
-        <v>225000</v>
+        <v>130000</v>
       </c>
       <c r="R12" s="59" t="s">
         <v>17</v>
@@ -6359,11 +6343,11 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" s="47">
+        <f t="shared" si="1"/>
         <v>6</v>
-      </c>
-      <c r="F13" s="47">
-        <f t="shared" si="1"/>
-        <v>8</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="51">
@@ -6375,7 +6359,7 @@
       </c>
       <c r="J13" s="32"/>
       <c r="K13" s="2">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -6383,60 +6367,58 @@
         <v>40000</v>
       </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="80">
-        <v>45000</v>
-      </c>
+      <c r="P13" s="42"/>
       <c r="Q13" s="11">
         <f t="shared" si="3"/>
-        <v>250000</v>
+        <v>155000</v>
       </c>
       <c r="R13" s="59" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A14" s="34">
-        <v>1</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="45">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D14" s="36">
-        <v>2</v>
-      </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="48">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G14" s="37">
-        <v>1</v>
-      </c>
-      <c r="H14" s="52">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I14" s="38">
-        <v>15000</v>
-      </c>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40">
-        <v>25000</v>
-      </c>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40">
+      <c r="A14" s="12">
+        <v>1</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>5</v>
+      </c>
+      <c r="F14" s="47">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>15000</v>
+      </c>
+      <c r="J14" s="32"/>
+      <c r="K14" s="2">
+        <v>125000</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2">
         <v>40000</v>
       </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="81">
+      <c r="O14" s="10"/>
+      <c r="P14" s="10">
         <v>45000</v>
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="3"/>
-        <v>125000</v>
+        <v>225000</v>
       </c>
       <c r="R14" s="59" t="s">
         <v>17</v>
@@ -6447,103 +6429,103 @@
         <v>1</v>
       </c>
       <c r="B15" s="28"/>
-      <c r="C15" s="46">
+      <c r="C15" s="44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="49">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G15" s="5">
-        <v>2</v>
-      </c>
-      <c r="H15" s="53">
-        <f t="shared" si="2"/>
-        <v>2</v>
+      <c r="E15" s="4">
+        <v>6</v>
+      </c>
+      <c r="F15" s="47">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="51">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>15000</v>
       </c>
       <c r="J15" s="32"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2">
-        <v>50000</v>
-      </c>
+      <c r="K15" s="2">
+        <v>150000</v>
+      </c>
+      <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2">
         <v>40000</v>
       </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="80">
+      <c r="O15" s="10"/>
+      <c r="P15" s="10">
         <v>45000</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="R15" s="59" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16" s="13">
-        <v>1</v>
-      </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="44">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="47">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G16" s="5">
-        <v>3</v>
-      </c>
-      <c r="H16" s="51">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I16" s="2">
-        <v>15000</v>
-      </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="2"/>
+      <c r="A16" s="34">
+        <v>1</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D16" s="36">
+        <v>2</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G16" s="37">
+        <v>1</v>
+      </c>
+      <c r="H16" s="52">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="38">
+        <v>15000</v>
+      </c>
+      <c r="J16" s="39"/>
+      <c r="K16" s="40"/>
       <c r="L16" s="40">
-        <v>75000</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="10">
-        <v>60000</v>
-      </c>
-      <c r="P16" s="10">
+        <v>25000</v>
+      </c>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40">
+        <v>40000</v>
+      </c>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41">
         <v>45000</v>
       </c>
       <c r="Q16" s="11">
         <f t="shared" si="3"/>
-        <v>195000</v>
+        <v>125000</v>
       </c>
       <c r="R16" s="59" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>1</v>
       </c>
       <c r="B17" s="28"/>
-      <c r="C17" s="44">
+      <c r="C17" s="46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6551,36 +6533,36 @@
         <v>2</v>
       </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="47">
+      <c r="F17" s="49">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G17" s="5">
-        <v>4</v>
-      </c>
-      <c r="H17" s="51">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I17" s="8">
+        <v>2</v>
+      </c>
+      <c r="H17" s="53">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I17" s="2">
         <v>15000</v>
       </c>
       <c r="J17" s="32"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="10">
-        <v>60000</v>
-      </c>
-      <c r="P17" s="41">
+      <c r="N17" s="2">
+        <v>40000</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="P17" s="10">
         <v>45000</v>
       </c>
       <c r="Q17" s="11">
         <f t="shared" si="3"/>
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="R17" s="59" t="s">
         <v>17</v>
@@ -6604,11 +6586,11 @@
         <v>2</v>
       </c>
       <c r="G18" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="51">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2">
         <v>15000</v>
@@ -6616,7 +6598,7 @@
       <c r="J18" s="32"/>
       <c r="K18" s="2"/>
       <c r="L18" s="40">
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -6628,18 +6610,18 @@
       </c>
       <c r="Q18" s="11">
         <f t="shared" si="3"/>
-        <v>245000</v>
+        <v>195000</v>
       </c>
       <c r="R18" s="59" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>1</v>
       </c>
       <c r="B19" s="28"/>
-      <c r="C19" s="46">
+      <c r="C19" s="44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -6647,222 +6629,214 @@
         <v>2</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="49">
+      <c r="F19" s="47">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G19" s="5">
-        <v>6</v>
-      </c>
-      <c r="H19" s="53">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="51">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I19" s="8">
         <v>15000</v>
       </c>
       <c r="J19" s="32"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="10">
         <v>60000</v>
       </c>
-      <c r="P19" s="73">
-        <v>45000</v>
-      </c>
-      <c r="Q19" s="62">
+      <c r="P19" s="41">
+        <v>45000</v>
+      </c>
+      <c r="Q19" s="11">
+        <f t="shared" si="3"/>
+        <v>220000</v>
+      </c>
+      <c r="R19" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A20" s="13">
+        <v>1</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="47">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G20" s="5">
+        <v>5</v>
+      </c>
+      <c r="H20" s="51">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J20" s="32"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="40">
+        <v>125000</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="10">
+        <v>60000</v>
+      </c>
+      <c r="P20" s="10">
+        <v>45000</v>
+      </c>
+      <c r="Q20" s="11">
+        <f t="shared" si="3"/>
+        <v>245000</v>
+      </c>
+      <c r="R20" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A21" s="13">
+        <v>1</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="49">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G21" s="5">
+        <v>6</v>
+      </c>
+      <c r="H21" s="53">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I21" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J21" s="32"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2">
+        <v>150000</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="10">
+        <v>60000</v>
+      </c>
+      <c r="P21" s="73">
+        <v>45000</v>
+      </c>
+      <c r="Q21" s="62">
         <f t="shared" si="3"/>
         <v>270000</v>
       </c>
-      <c r="R19" s="59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A20" s="34">
-        <v>1</v>
-      </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="45">
-        <f t="shared" ref="C20:C24" si="4">SUM(A20:B20)</f>
-        <v>1</v>
-      </c>
-      <c r="D20" s="69">
-        <v>2</v>
-      </c>
-      <c r="E20" s="69">
-        <v>1</v>
-      </c>
-      <c r="F20" s="48">
-        <f t="shared" ref="F20:F24" si="5">SUM(D20:E20)</f>
+      <c r="R21" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A22" s="34">
+        <v>1</v>
+      </c>
+      <c r="B22" s="68"/>
+      <c r="C22" s="45">
+        <f t="shared" ref="C22:C26" si="12">SUM(A22:B22)</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="69">
+        <v>2</v>
+      </c>
+      <c r="E22" s="69">
+        <v>1</v>
+      </c>
+      <c r="F22" s="48">
+        <f t="shared" ref="F22:F26" si="13">SUM(D22:E22)</f>
         <v>3</v>
       </c>
-      <c r="G20" s="70">
-        <v>1</v>
-      </c>
-      <c r="H20" s="52">
-        <f t="shared" ref="H20:H24" si="6">SUM(G20:G20)</f>
-        <v>1</v>
-      </c>
-      <c r="I20" s="2">
-        <v>15000</v>
-      </c>
-      <c r="J20" s="71"/>
-      <c r="K20" s="38">
+      <c r="G22" s="70">
+        <v>1</v>
+      </c>
+      <c r="H22" s="52">
+        <f t="shared" ref="H22:H26" si="14">SUM(G22:G22)</f>
+        <v>1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J22" s="71"/>
+      <c r="K22" s="38">
         <v>25000</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L22" s="38">
         <v>25000</v>
       </c>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38">
+      <c r="M22" s="38"/>
+      <c r="N22" s="38">
         <v>40000</v>
       </c>
-      <c r="O20" s="72"/>
-      <c r="P20" s="10">
-        <v>45000</v>
-      </c>
-      <c r="Q20" s="11">
-        <f t="shared" ref="Q20:Q24" si="7">SUM(I20:P20)</f>
+      <c r="O22" s="72"/>
+      <c r="P22" s="10">
+        <v>45000</v>
+      </c>
+      <c r="Q22" s="11">
+        <f t="shared" ref="Q22:Q26" si="15">SUM(I22:P22)</f>
         <v>150000</v>
       </c>
-      <c r="R20" s="58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="13">
-        <v>1</v>
-      </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="46">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1</v>
-      </c>
-      <c r="F21" s="49">
-        <f t="shared" si="5"/>
+      <c r="R22" s="58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A23" s="13">
+        <v>1</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="46">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="49">
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
-      <c r="G21" s="5">
-        <v>2</v>
-      </c>
-      <c r="H21" s="53">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="I21" s="2">
-        <v>15000</v>
-      </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="2">
-        <v>25000</v>
-      </c>
-      <c r="L21" s="2">
-        <v>50000</v>
-      </c>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2">
-        <v>40000</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="73">
-        <v>45000</v>
-      </c>
-      <c r="Q21" s="11">
-        <f t="shared" si="7"/>
-        <v>175000</v>
-      </c>
-      <c r="R21" s="59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A22" s="13">
-        <v>1</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="44">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1</v>
-      </c>
-      <c r="F22" s="47">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="G22" s="5">
-        <v>3</v>
-      </c>
-      <c r="H22" s="51">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="I22" s="2">
-        <v>15000</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="2">
-        <v>25000</v>
-      </c>
-      <c r="L22" s="40">
-        <v>75000</v>
-      </c>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="10">
-        <v>60000</v>
-      </c>
-      <c r="P22" s="10">
-        <v>45000</v>
-      </c>
-      <c r="Q22" s="11">
-        <f t="shared" si="7"/>
-        <v>220000</v>
-      </c>
-      <c r="R22" s="59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="12">
-        <v>1</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="44">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="4">
-        <v>1</v>
-      </c>
-      <c r="F23" s="47">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
       <c r="G23" s="5">
-        <v>4</v>
-      </c>
-      <c r="H23" s="51">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H23" s="53">
+        <f t="shared" si="14"/>
+        <v>2</v>
       </c>
       <c r="I23" s="2">
         <v>15000</v>
@@ -6872,19 +6846,19 @@
         <v>25000</v>
       </c>
       <c r="L23" s="2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="10">
-        <v>60000</v>
-      </c>
+      <c r="N23" s="2">
+        <v>40000</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" s="73">
         <v>45000</v>
       </c>
       <c r="Q23" s="11">
-        <f t="shared" si="7"/>
-        <v>245000</v>
+        <f t="shared" si="15"/>
+        <v>175000</v>
       </c>
       <c r="R23" s="59" t="s">
         <v>17</v>
@@ -6896,7 +6870,7 @@
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D24" s="4">
@@ -6906,15 +6880,15 @@
         <v>1</v>
       </c>
       <c r="F24" s="47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="G24" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" s="51">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="14"/>
+        <v>3</v>
       </c>
       <c r="I24" s="2">
         <v>15000</v>
@@ -6924,7 +6898,7 @@
         <v>25000</v>
       </c>
       <c r="L24" s="40">
-        <v>125000</v>
+        <v>75000</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -6935,60 +6909,60 @@
         <v>45000</v>
       </c>
       <c r="Q24" s="11">
-        <f t="shared" si="7"/>
-        <v>270000</v>
+        <f t="shared" si="15"/>
+        <v>220000</v>
       </c>
       <c r="R24" s="59" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A25" s="34">
-        <v>1</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="45">
-        <f t="shared" ref="C25:C28" si="8">SUM(A25:B25)</f>
-        <v>1</v>
-      </c>
-      <c r="D25" s="36">
-        <v>2</v>
-      </c>
-      <c r="E25" s="36">
-        <v>2</v>
-      </c>
-      <c r="F25" s="48">
-        <f t="shared" ref="F25:F28" si="9">SUM(D25:E25)</f>
+      <c r="A25" s="12">
+        <v>1</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="44">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="47">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="G25" s="5">
         <v>4</v>
       </c>
-      <c r="G25" s="37">
-        <v>1</v>
-      </c>
-      <c r="H25" s="52">
-        <f t="shared" ref="H25:H28" si="10">SUM(G25:G25)</f>
-        <v>1</v>
+      <c r="H25" s="51">
+        <f t="shared" si="14"/>
+        <v>4</v>
       </c>
       <c r="I25" s="2">
         <v>15000</v>
       </c>
-      <c r="J25" s="39"/>
-      <c r="K25" s="40">
-        <v>50000</v>
-      </c>
-      <c r="L25" s="40">
+      <c r="J25" s="32"/>
+      <c r="K25" s="2">
         <v>25000</v>
       </c>
-      <c r="M25" s="40"/>
-      <c r="N25" s="40">
-        <v>40000</v>
-      </c>
-      <c r="O25" s="41"/>
+      <c r="L25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="10">
+        <v>60000</v>
+      </c>
       <c r="P25" s="73">
         <v>45000</v>
       </c>
       <c r="Q25" s="11">
-        <f t="shared" ref="Q25:Q28" si="11">SUM(I25:P25)</f>
-        <v>175000</v>
+        <f t="shared" si="15"/>
+        <v>245000</v>
       </c>
       <c r="R25" s="59" t="s">
         <v>17</v>
@@ -6999,167 +6973,271 @@
         <v>1</v>
       </c>
       <c r="B26" s="28"/>
-      <c r="C26" s="46">
-        <f t="shared" si="8"/>
+      <c r="C26" s="44">
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="D26" s="4">
         <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>2</v>
-      </c>
-      <c r="F26" s="49">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F26" s="47">
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="G26" s="5">
-        <v>2</v>
-      </c>
-      <c r="H26" s="53">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="H26" s="51">
+        <f t="shared" si="14"/>
+        <v>5</v>
       </c>
       <c r="I26" s="2">
         <v>15000</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="2">
+        <v>25000</v>
+      </c>
+      <c r="L26" s="40">
+        <v>125000</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="10">
+        <v>60000</v>
+      </c>
+      <c r="P26" s="10">
+        <v>45000</v>
+      </c>
+      <c r="Q26" s="11">
+        <f t="shared" si="15"/>
+        <v>270000</v>
+      </c>
+      <c r="R26" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A27" s="34">
+        <v>1</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="45">
+        <f t="shared" ref="C27:C30" si="16">SUM(A27:B27)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="36">
+        <v>2</v>
+      </c>
+      <c r="E27" s="36">
+        <v>2</v>
+      </c>
+      <c r="F27" s="48">
+        <f t="shared" ref="F27:F30" si="17">SUM(D27:E27)</f>
+        <v>4</v>
+      </c>
+      <c r="G27" s="37">
+        <v>1</v>
+      </c>
+      <c r="H27" s="52">
+        <f t="shared" ref="H27:H30" si="18">SUM(G27:G27)</f>
+        <v>1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J27" s="39"/>
+      <c r="K27" s="40">
         <v>50000</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L27" s="40">
+        <v>25000</v>
+      </c>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40">
+        <v>40000</v>
+      </c>
+      <c r="O27" s="41"/>
+      <c r="P27" s="73">
+        <v>45000</v>
+      </c>
+      <c r="Q27" s="11">
+        <f t="shared" ref="Q27:Q30" si="19">SUM(I27:P27)</f>
+        <v>175000</v>
+      </c>
+      <c r="R27" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A28" s="13">
+        <v>1</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="46">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="49">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="53">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J28" s="32"/>
+      <c r="K28" s="2">
         <v>50000</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2">
+      <c r="L28" s="2">
+        <v>50000</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2">
         <v>40000</v>
       </c>
-      <c r="O26" s="2"/>
-      <c r="P26" s="10">
-        <v>45000</v>
-      </c>
-      <c r="Q26" s="11">
-        <f t="shared" si="11"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="10">
+        <v>45000</v>
+      </c>
+      <c r="Q28" s="11">
+        <f t="shared" si="19"/>
         <v>200000</v>
       </c>
-      <c r="R26" s="59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A27" s="13">
-        <v>1</v>
-      </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="44">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="D27" s="4">
-        <v>2</v>
-      </c>
-      <c r="E27" s="4">
-        <v>2</v>
-      </c>
-      <c r="F27" s="47">
-        <f t="shared" si="9"/>
+      <c r="R28" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A29" s="13">
+        <v>1</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="44">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
+        <v>2</v>
+      </c>
+      <c r="F29" s="47">
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G29" s="5">
         <v>3</v>
       </c>
-      <c r="H27" s="51">
-        <f t="shared" si="10"/>
+      <c r="H29" s="51">
+        <f t="shared" si="18"/>
         <v>3</v>
       </c>
-      <c r="I27" s="2">
-        <v>15000</v>
-      </c>
-      <c r="J27" s="32"/>
-      <c r="K27" s="2">
+      <c r="I29" s="2">
+        <v>15000</v>
+      </c>
+      <c r="J29" s="32"/>
+      <c r="K29" s="2">
         <v>50000</v>
       </c>
-      <c r="L27" s="40">
+      <c r="L29" s="40">
         <v>75000</v>
       </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="10">
-        <v>60000</v>
-      </c>
-      <c r="P27" s="73">
-        <v>45000</v>
-      </c>
-      <c r="Q27" s="11">
-        <f t="shared" si="11"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="10">
+        <v>60000</v>
+      </c>
+      <c r="P29" s="73">
+        <v>45000</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="19"/>
         <v>245000</v>
       </c>
-      <c r="R27" s="59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="14">
-        <v>1</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="74">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>2</v>
-      </c>
-      <c r="F28" s="64">
-        <f t="shared" si="9"/>
+      <c r="R29" s="59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="14">
+        <v>1</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="74">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="D30" s="15">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>2</v>
+      </c>
+      <c r="F30" s="64">
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G30" s="16">
         <v>4</v>
       </c>
-      <c r="H28" s="65">
-        <f t="shared" si="10"/>
+      <c r="H30" s="65">
+        <f t="shared" si="18"/>
         <v>4</v>
       </c>
-      <c r="I28" s="17">
-        <v>15000</v>
-      </c>
-      <c r="J28" s="33"/>
-      <c r="K28" s="17">
+      <c r="I30" s="17">
+        <v>15000</v>
+      </c>
+      <c r="J30" s="33"/>
+      <c r="K30" s="17">
         <v>50000</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L30" s="17">
         <v>100000</v>
       </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="19">
-        <v>60000</v>
-      </c>
-      <c r="P28" s="10">
-        <v>45000</v>
-      </c>
-      <c r="Q28" s="66">
-        <f t="shared" si="11"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="19">
+        <v>60000</v>
+      </c>
+      <c r="P30" s="10">
+        <v>45000</v>
+      </c>
+      <c r="Q30" s="66">
+        <f t="shared" si="19"/>
         <v>270000</v>
       </c>
-      <c r="R28" s="60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="P29" s="75" t="s">
+      <c r="R30" s="60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="P31" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
+      <c r="Q31" s="77"/>
+      <c r="R31" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="P31:R31"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/マイク料金表.xlsx
+++ b/マイク料金表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SLTY\Desktop\mic-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BD4A03-7326-4696-AAF7-AA906BA92BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9105D601-16B2-45C1-9AFA-617B1A937E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{BD0FD287-6373-454C-8CFD-DB7F90A907F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD0FD287-6373-454C-8CFD-DB7F90A907F7}"/>
   </bookViews>
   <sheets>
     <sheet name="ボールルーム" sheetId="1" r:id="rId1"/>
@@ -3845,17 +3845,17 @@
         <v>125000</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2">
+        <v>40000</v>
+      </c>
       <c r="L7" s="10"/>
       <c r="M7" s="2">
         <v>45000</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="2"/>
-        <v>195000</v>
+        <v>225000</v>
       </c>
       <c r="O7" s="59" t="s">
         <v>17</v>
@@ -3887,17 +3887,17 @@
         <v>150000</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="2">
-        <v>10000</v>
-      </c>
-      <c r="K8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2">
+        <v>40000</v>
+      </c>
       <c r="L8" s="10"/>
       <c r="M8" s="2">
         <v>45000</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="2"/>
-        <v>220000</v>
+        <v>250000</v>
       </c>
       <c r="O8" s="59" t="s">
         <v>17</v>
@@ -4913,17 +4913,17 @@
       </c>
       <c r="L7" s="32"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>10000</v>
-      </c>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
+        <v>40000</v>
+      </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="2">
         <v>45000</v>
       </c>
       <c r="R7" s="11">
         <f t="shared" si="2"/>
-        <v>155000</v>
+        <v>185000</v>
       </c>
       <c r="S7" s="59" t="s">
         <v>17</v>
@@ -4963,17 +4963,17 @@
       </c>
       <c r="L8" s="32"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2">
-        <v>10000</v>
-      </c>
-      <c r="O8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2">
+        <v>40000</v>
+      </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="2">
         <v>45000</v>
       </c>
       <c r="R8" s="11">
         <f t="shared" si="2"/>
-        <v>180000</v>
+        <v>210000</v>
       </c>
       <c r="S8" s="59" t="s">
         <v>17</v>

--- a/マイク料金表.xlsx
+++ b/マイク料金表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9105D601-16B2-45C1-9AFA-617B1A937E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD0FD287-6373-454C-8CFD-DB7F90A907F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{BD0FD287-6373-454C-8CFD-DB7F90A907F7}"/>
   </bookViews>
   <sheets>
     <sheet name="ボールルーム" sheetId="1" r:id="rId1"/>
